--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -1,26 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2479651_cognizant_com/Documents/Desktop/JAVA codes/identify-new-bikes/src/test/resources/testdata/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="73" documentId="11_DD356BBA5AE42649C66EF6AF940BA14AB32D4750" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4EC362E-2A8F-4DB4-B47D-B5331264C174}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="UpcomingHondaBikes" sheetId="1" r:id="rId1"/>
+    <sheet name="UsedCarsChennai" sheetId="2" r:id="rId2"/>
+    <sheet name="GoogleLoginTestData" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>Bike Name</t>
+  </si>
+  <si>
+    <t>Expected Price (INR)</t>
+  </si>
+  <si>
+    <t>Expected Launch Date</t>
+  </si>
+  <si>
+    <t>Honda</t>
+  </si>
+  <si>
+    <t>Honda CRF300L</t>
+  </si>
+  <si>
+    <t>August 2026</t>
+  </si>
+  <si>
+    <t>Honda CB300F</t>
+  </si>
+  <si>
+    <t>July 2026</t>
+  </si>
+  <si>
+    <t>Honda NX500</t>
+  </si>
+  <si>
+    <t>September 2026</t>
+  </si>
+  <si>
+    <t>Honda Activa Electric</t>
+  </si>
+  <si>
+    <t>October 2026</t>
+  </si>
+  <si>
+    <t>Honda CB500X</t>
+  </si>
+  <si>
+    <t>November 2026</t>
+  </si>
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>Popular Model</t>
+  </si>
+  <si>
+    <t>Maruti Swift</t>
+  </si>
+  <si>
+    <t>Hyundai i20</t>
+  </si>
+  <si>
+    <t>Honda City</t>
+  </si>
+  <si>
+    <t>Maruti Baleno</t>
+  </si>
+  <si>
+    <t>Hyundai Creta</t>
+  </si>
+  <si>
+    <t>Tata Nexon</t>
+  </si>
+  <si>
+    <t>Kia Seltos</t>
+  </si>
+  <si>
+    <t>Toyota Innova</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Email / Username</t>
+  </si>
+  <si>
+    <t>Expected Error Message</t>
+  </si>
+  <si>
+    <t>TC_001</t>
+  </si>
+  <si>
+    <t>Invalid Email Format</t>
+  </si>
+  <si>
+    <t>invaliduser@@gmail</t>
+  </si>
+  <si>
+    <t>Couldn't find your Google Account</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>Non-existent Account</t>
+  </si>
+  <si>
+    <t>nonexistentuser9999xyz@gmail.com</t>
+  </si>
+  <si>
+    <t>TC_003</t>
+  </si>
+  <si>
+    <t>Empty Email Field</t>
+  </si>
+  <si>
+    <t>Enter an email or phone number</t>
+  </si>
+  <si>
+    <t>TC_004</t>
+  </si>
+  <si>
+    <t>Special Characters Only</t>
+  </si>
+  <si>
+    <t>!@#$%^&amp;*()</t>
+  </si>
+  <si>
+    <t>TC_005</t>
+  </si>
+  <si>
+    <t>Spaces in Email</t>
+  </si>
+  <si>
+    <t>invalid user@gmail.com</t>
+  </si>
+  <si>
+    <t>Actual Price (INR)</t>
+  </si>
+  <si>
+    <t>Actual Bike Name</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Actual models</t>
+  </si>
+  <si>
+    <t>Actual Error Message</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +186,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF8F00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,18 +234,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -79,44 +304,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -143,15 +368,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -178,7 +402,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -190,150 +413,512 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="3" width="25" customWidth="1"/>
+    <col min="4" max="7" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="6">
+        <v>300000</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="6">
+        <v>250000</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="6">
+        <v>350000</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="6">
+        <v>110000</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="6">
+        <v>380000</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="6" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2479651_cognizant_com/Documents/Desktop/JAVA codes/identify-new-bikes/src/test/resources/testdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2480341\IdeaProjects\identify-new-bikes\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="11_DD356BBA5AE42649C66EF6AF940BA14AB32D4750" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4EC362E-2A8F-4DB4-B47D-B5331264C174}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACAC96C5-848D-4969-A83E-9D31A7D83DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,9 +129,6 @@
     <t>Non-existent Account</t>
   </si>
   <si>
-    <t>nonexistentuser9999xyz@gmail.com</t>
-  </si>
-  <si>
     <t>TC_003</t>
   </si>
   <si>
@@ -172,13 +169,16 @@
   </si>
   <si>
     <t>Actual Error Message</t>
+  </si>
+  <si>
+    <t>nonexistentuser9999xyz@gma.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +195,14 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -250,8 +258,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -270,14 +279,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -594,19 +604,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -617,14 +627,14 @@
         <v>5</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="6">
+      <c r="D2" s="2">
         <v>300000</v>
       </c>
-      <c r="E2" s="6"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -634,14 +644,14 @@
         <v>7</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="6">
+      <c r="D3" s="2">
         <v>250000</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="7"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -651,14 +661,14 @@
         <v>9</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="6">
+      <c r="D4" s="2">
         <v>350000</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="7"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
@@ -668,14 +678,14 @@
         <v>11</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="6">
+      <c r="D5" s="2">
         <v>110000</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="7"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
@@ -685,14 +695,14 @@
         <v>13</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="6">
+      <c r="D6" s="2">
         <v>380000</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -718,10 +728,10 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -834,10 +844,10 @@
         <v>28</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -863,8 +873,8 @@
       <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>35</v>
+      <c r="C3" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>32</v>
@@ -874,27 +884,27 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>32</v>
@@ -904,13 +914,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>32</v>
@@ -919,6 +929,9 @@
       <c r="F6" s="5"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{99C6A257-59F1-4353-A534-6643FD16B705}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>